--- a/public/sablon/kulalilar-afis-sablonu.xlsx
+++ b/public/sablon/kulalilar-afis-sablonu.xlsx
@@ -913,7 +913,7 @@
       <formula1>"E"</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Geçersiz değer" error="Bu sütunda yalnız listedeki değerler kullanılabilir." type="list">
-      <formula1>"1,2,3,4"</formula1>
+      <formula1>"1,2,3,4,6,8"</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Geçersiz değer" error="Bu sütunda yalnız listedeki değerler kullanılabilir." type="list">
       <formula1>"NÖTR KÂĞIT,NÖTR AÇIK,NÖTR ORTA,NÖTR KOYU,NÖTR SİYAH,SICAK KÂĞIT,SICAK AÇIK,SICAK ORTA,SICAK KOYU,SICAK SİYAH,ZEYTİN KÂĞIT,ZEYTİN AÇIK,ZEYTİN ORTA,ZEYTİN KOYU,ZEYTİN SİYAH"</formula1>
@@ -960,7 +960,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>· Aynı SAYFA numarasına yazdığın satırlar tek afiş olur. 4'ten fazlaysa kendiliğinden bölünür.</t>
+          <t>· Aynı SAYFA numarasına yazdığın satırlar tek afiş olur. ÜRÜN SAYISI'ndan fazlaysa kendiliğinden bölünür.</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Sayfada kaç ürün olsun (1-4). Boşsa satır sayısından hesaplanır.</t>
+          <t>Sayfada kaç ürün olsun: 1-4 · 6 · 8. Boşsa satır sayısından hesaplanır.</t>
         </is>
       </c>
     </row>
